--- a/ResourcesBD/ProductEnrichment.xlsx
+++ b/ResourcesBD/ProductEnrichment.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Product ID</t>
   </si>
@@ -118,6 +118,39 @@
   </si>
   <si>
     <t>AUTO_PROD2CCA</t>
+  </si>
+  <si>
+    <t>AUTO_PROD87E1</t>
+  </si>
+  <si>
+    <t>AUTO_PROD6D99</t>
+  </si>
+  <si>
+    <t>AUTO_PRODB440</t>
+  </si>
+  <si>
+    <t>AUTO_PROD9369</t>
+  </si>
+  <si>
+    <t>AUTO_PRODF3A3</t>
+  </si>
+  <si>
+    <t>AUTO_PRODD081</t>
+  </si>
+  <si>
+    <t>AUTO_PRODFC73</t>
+  </si>
+  <si>
+    <t>AUTO_PROD5826</t>
+  </si>
+  <si>
+    <t>AUTO_PROD16BA</t>
+  </si>
+  <si>
+    <t>AUTO_PROD0275</t>
+  </si>
+  <si>
+    <t>AUTO_PRODA362</t>
   </si>
 </sst>
 </file>
@@ -490,7 +523,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>11</v>
